--- a/tools/doc-pol_new.xlsx
+++ b/tools/doc-pol_new.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ericlaubacher/Documents/GitHub/ciso-assistant-community/tools/excel/intuitem/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ciso\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86D37534-4DC1-DE42-868D-882B1DFBB7B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6B9D3A5-D92B-4699-B0E0-179179FCBE68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="34560" windowHeight="20400" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="library_meta" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="770" uniqueCount="525">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="947" uniqueCount="687">
   <si>
     <t>type</t>
   </si>
@@ -45,9 +45,6 @@
     <t>version</t>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
     <t>locale</t>
   </si>
   <si>
@@ -73,9 +70,6 @@
   </si>
   <si>
     <t>copyright</t>
-  </si>
-  <si>
-    <t>© intuitem - 2024</t>
   </si>
   <si>
     <t>provider</t>
@@ -612,9 +606,6 @@
     <t>Registre des accès à privilèges</t>
   </si>
   <si>
-    <t>DOC.INCIDENT_REGiSTER</t>
-  </si>
-  <si>
     <t>Security Incident Register</t>
   </si>
   <si>
@@ -775,17 +766,6 @@
   </si>
   <si>
     <t>Information classification and handling policy</t>
-  </si>
-  <si>
-    <t>classification
-protection and handling of information
-Poritection and handling of PII
-clear desk
-clear screen
-Protection of records
-Retention rules
-Use of test information
-Continual improvement</t>
   </si>
   <si>
     <t>A.5.12, A.5.13
@@ -2075,12 +2055,720 @@
   <si>
     <t>L'authentification multifacteur (MFA) améliore la sécurité en exigeant deux facteurs de vérification issus de catégories différentes : ce que vous savez (ex. : un mot de passe), ce que vous possédez (ex. : un jeton ou un smartphone) et ce que vous êtes (ex. : une empreinte digitale ou une reconnaissance faciale)</t>
   </si>
+  <si>
+    <t>name[de]</t>
+  </si>
+  <si>
+    <t>description[de]</t>
+  </si>
+  <si>
+    <t>Übliche Referenzkontrollen</t>
+  </si>
+  <si>
+    <t>Übliche Dokumente, Richtlinien, Verfahren, Schulungen und technischen Kontrollen, die von intuitem empfohlen werden</t>
+  </si>
+  <si>
+    <t>Dokument zur Organisationsübersicht</t>
+  </si>
+  <si>
+    <t>Ziele der Organisation
+Organigramm
+ISMS-Ziele
+Verantwortlichkeiten des CISO
+Managementbewertung des ISMS</t>
+  </si>
+  <si>
+    <t>Interessierte Parteien
+Behörden
+Fach- und Interessengruppen</t>
+  </si>
+  <si>
+    <t>Produkte und Dienstleistungen
+Produkte und Dienstleistungen mit Zertifizierungspflicht
+Standorte
+Organisationssicht
+Sicht der Geschäftsarchitektur
+Sicht der Datenarchitektur
+Sicht der Applikationsarchitektur
+Sicht der Technologiearchitektur
+Netzwerksicht
+Beschreibung des Geltungsbereichs</t>
+  </si>
+  <si>
+    <t>Gesetzliche Anforderungen
+Behördliche bzw. gesetzliche Vorgaben
+Regulatorische Anforderungen
+Vertragliche Anforderungen
+Rechte an geistigem Eigentum
+Arbeitsverträge
+Geheimhaltungsvereinbarungen (NDAs)</t>
+  </si>
+  <si>
+    <t>Dokument zum Kontext der Organisation</t>
+  </si>
+  <si>
+    <t>Dokument zum Geltungsbereich des ISMS</t>
+  </si>
+  <si>
+    <t>Rechtskataster</t>
+  </si>
+  <si>
+    <t>Dokument zur Geltungsbereichserklärung (SoA)</t>
+  </si>
+  <si>
+    <t>Verantwortlichkeitsmatrix für Kontrollen</t>
+  </si>
+  <si>
+    <t>Auditplan-Dokument</t>
+  </si>
+  <si>
+    <t>Kontext der Organisation
+Führung
+Planung
+Unterstützung
+Betrieb
+Leistungsbewertung
+Verbesserung
+Organisatorische Kontrollen
+Personenbezogene Kontrollen
+Physische Kontrollen
+Technologische Kontrollen</t>
+  </si>
+  <si>
+    <t>Kompetenzmatrix</t>
+  </si>
+  <si>
+    <t>Verantwortlichkeitsmatrix</t>
+  </si>
+  <si>
+    <t>RACI für das ISMS</t>
+  </si>
+  <si>
+    <t>Kommunikationsplan-Dokument</t>
+  </si>
+  <si>
+    <t>Risikoregister</t>
+  </si>
+  <si>
+    <t>Risiko-Verantwortlicher
+Auswirkung
+Eintrittswahrscheinlichkeit
+Risikostufe
+Bewertung
+Priorität
+Behandlungsoption
+Minderungsmaßnahmen – empfohlene Sicherheitsmaßnahmen</t>
+  </si>
+  <si>
+    <t>Register für Sicherheitsziele</t>
+  </si>
+  <si>
+    <t>Überprüfung der Risiken
+Überprüfung der Sicherheitsziele
+Überprüfung von Sicherheitsvorfällen
+Überprüfung des Schwachstellenmanagements
+Überprüfung der Nichtkonformitäten</t>
+  </si>
+  <si>
+    <t>Schulungs- und Bewusstseinsregister</t>
+  </si>
+  <si>
+    <t>Dokumentenregister</t>
+  </si>
+  <si>
+    <t>Regeln für Erstellung und Pflege
+Versionskontrolle
+Register
+Kontinuierliche Verbesserung</t>
+  </si>
+  <si>
+    <t>Register für operative Verfahren</t>
+  </si>
+  <si>
+    <t>Protokoll der Nichtkonformitäten</t>
+  </si>
+  <si>
+    <t>Liste der Nichtkonformitäten (Vorfall, Probleme, …)
+Ergriffene Korrekturmaßnahmen</t>
+  </si>
+  <si>
+    <t>Verfahrensregelwerk</t>
+  </si>
+  <si>
+    <t>Asset-Register</t>
+  </si>
+  <si>
+    <t>Lieferantenregister</t>
+  </si>
+  <si>
+    <t>Risikomanagement</t>
+  </si>
+  <si>
+    <t>Plan für Informationssicherheitsbewusstsein und Schulungen</t>
+  </si>
+  <si>
+    <t>Zielsetzung: Sensibilisierung aller Mitarbeitenden sowie gezielte Schulungen für relevante Rollen, um sicheres Verhalten zu fördern, Compliance sicherzustellen und Risiken zu reduzieren.
+Geltungsbereich: Sensibilisierung für alle Mitarbeitenden und Auftragnehmer; zielgerichtete Schulungen für spezifische Teams (z. B. IT, Sicherheit, Zugriffsadministration).
+Rollen und Verantwortlichkeiten: Verantwortung wird IT-, HR- und Sicherheitsteams zugewiesen.
+Schulungsanforderungen: Festlegung verpflichtender Themen (z. B. Zugriffsmanagement, sichere Konfigurationen) und Häufigkeiten (z. B. jährlich, Onboarding).
+Bereitstellungsmethoden: Sensibilisierung über E-Learning und Kampagnen; Schulungen über praxisorientierte Workshops und Simulationen.
+Evaluation: Nachverfolgung der Teilnahmequoten, Quiz-Ergebnisse und Phishing-Testresultate.
+Compliance: Ausrichtung an relevanten Vorschriften (z. B. DSGVO, ISO 27001) und Aufrechterhaltung prüfbereiter Nachweise.
+Kontinuierliche Verbesserung: Aktualisierung auf Basis von Feedback und neuen Bedrohungen.</t>
+  </si>
+  <si>
+    <t>Sicherheitsnachweisplan</t>
+  </si>
+  <si>
+    <t>Ein von Lieferanten bereitgestelltes Dokument, das Sicherheitsmaßnahmen, die Einhaltung von Standards (z. B. ISO 27001) und Prüfverfahren beschreibt, um die Sicherheit ihrer Produkte, Dienstleistungen oder Systeme sicherzustellen. Es zeigt das Engagement für eine sichere Umgebung und liefert Nachweise zur Einhaltung und Umsetzung von Sicherheitspraktiken.</t>
+  </si>
+  <si>
+    <t>Systemabbild der Informationssysteme</t>
+  </si>
+  <si>
+    <t>Eine visuelle Darstellung der Komponenten des Informationssystems einer Organisation und ihrer Wechselwirkungen zur Verbesserung von Verwaltung und Sicherheit.</t>
+  </si>
+  <si>
+    <t>Register für privilegierte Zugangskonten</t>
+  </si>
+  <si>
+    <t>Register für Sicherheitsvorfälle</t>
+  </si>
+  <si>
+    <t>Flussmatrix</t>
+  </si>
+  <si>
+    <t>Ein Dokument, das autorisierte Datenflüsse zwischen Systemen, Anwendungen oder Netzwerkanwendungsbereichen abbildet, um eine sichere und regelkonforme Kommunikation sicherzustellen.</t>
+  </si>
+  <si>
+    <t>Grundsätze der Sicherheitsarchitektur</t>
+  </si>
+  <si>
+    <t>Verfahren zum Management privilegierter Zugänge</t>
+  </si>
+  <si>
+    <t>Ein Dokument, das die Prozesse und Kontrollen zur Verwaltung und Sicherung privilegierter Konten beschreibt und sicherstellt, dass nur autorisierte Benutzer Zugang zu kritischen Systemen und Daten haben; einschließlich Maßnahmen wie Monitoring, Audits und zeitlich begrenzten Zugriffsrechten zur Minimierung von Risiken.</t>
+  </si>
+  <si>
+    <t>Verfahren zur Rezertifizierung von Benutzerkonten</t>
+  </si>
+  <si>
+    <t>Ein Dokument, das den Prozess zur regelmäßigen Überprüfung und Validierung von Benutzerzugriffsrechten, Systemzertifizierungen oder der Einhaltung von Standards beschreibt. Es stellt sicher, dass nur autorisierte Benutzer und Systeme Zugriff oder Zertifizierungen behalten und unterstützt dabei, veraltete oder unnötige Berechtigungen zu identifizieren und zu widerrufen.</t>
+  </si>
+  <si>
+    <t>HR-Sicherheitsverfahren</t>
+  </si>
+  <si>
+    <t>Ein Dokument, das Prozesse und Kontrollen zur Verwaltung personalbezogener Sicherheitsaspekte innerhalb der Organisation beschreibt und die Einhaltung gesetzlicher, regulatorischer und sicherheitsrelevanter Standards sicherstellt. Es umfasst Verfahren zu Rekrutierung, Onboarding, Rollenänderungen, Schulungen und Austrittsprozessen, um Informationen und Vermögenswerte der Organisation zu schützen.</t>
+  </si>
+  <si>
+    <t>Physisches Sicherheitsverfahren</t>
+  </si>
+  <si>
+    <t>Zugangskontrolle: Verfahren zur Gewährung, zum Widerruf und zur Überwachung physischen Zugangs zu gesicherten Bereichen.
+Schutz von Vermögenswerten: Richtlinien zum Schutz kritischer Assets (z. B. Server, Speichersysteme).
+Überwachung: Einsatz von Kameras, Alarm- und Überwachungssystemen zur Erkennung und Verhinderung von Sicherheitsverletzungen.
+Besuchermanagement: Richtlinien zur Registrierung und Begleitung von Besuchern in gesicherten Bereichen.
+Reaktion auf Vorfälle: Vorgehensweisen zur Behandlung physischer Sicherheitsvorfälle oder Notfälle.</t>
+  </si>
+  <si>
+    <t>Verfahren für Gruppenrichtlinienobjekte (GPO)</t>
+  </si>
+  <si>
+    <t>Beschreibt, wie Gruppenrichtlinienobjekte erstellt, konfiguriert und verwaltet werden, um Sicherheitseinstellungen, Systemkonfigurationen und Benutzerregeln in einer Windows-Umgebung durchzusetzen. Es stellt eine konsistente Umsetzung organisatorischer Richtlinien für einen sicheren und regelkonformen IT-Betrieb sicher.</t>
+  </si>
+  <si>
+    <t>Verfahren für Update-Management</t>
+  </si>
+  <si>
+    <t>Rollen und Verantwortlichkeiten
+Klassifizierung von Updates
+Planung von Updates
+Tests und Validierung
+Bereitstellungsprozess
+Überwachung und Verifikation
+Dokumentation und Berichterstattung</t>
+  </si>
+  <si>
+    <t>Verfahren zum Incident-Management</t>
+  </si>
+  <si>
+    <t>Praktische Umsetzung der Richtlinie zum Incident-Management</t>
+  </si>
+  <si>
+    <t>Verfahren zur sicheren Entsorgung</t>
+  </si>
+  <si>
+    <t>Rollen und Verantwortlichkeiten
+Identifikation von Assets zur Entsorgung
+Methoden zur sicheren Entsorgung
+Datenbereinigung (Data Sanitization)
+Einhaltung gesetzlicher und regulatorischer Anforderungen
+Dokumentation und Aufbewahrung von Nachweisen
+Verifikation und Audit</t>
+  </si>
+  <si>
+    <t>Verfahren zur Zeitsynchronisation</t>
+  </si>
+  <si>
+    <t>Zeitquelle: Verwendung zuverlässiger externer Quellen (z. B. NTP-Server).
+Konfiguration: Festlegung von Synchronisationsintervallen und Fallback-Mechanismen.
+Überwachung: Regelmäßige Überprüfung des Status der Zeitsynchronisation.</t>
+  </si>
+  <si>
+    <t>Verfahren zur E-Mail-Sicherheitskonfiguration</t>
+  </si>
+  <si>
+    <t>Konfiguration des E-Mail-Servers
+Domänenbasierter E-Mail-Schutz
+Anti-Malware- und Anti-Spam-Kontrollen
+Verschlüsselung und sichere Kommunikation
+Zugriffskontrolle und Überwachung
+Backup und Wiederherstellung
+Sensibilisierung und Schulung der Benutzer</t>
+  </si>
+  <si>
+    <t>Verfahren zum Logging</t>
+  </si>
+  <si>
+    <t>Erfassung und Kategorisierung von Logdaten
+Sichere Speicherung und Aufbewahrungsrichtlinien
+Analyse zur Anomalieerkennung und Incident Response</t>
+  </si>
+  <si>
+    <t>Ziele der Informationssicherheit
+Verpflichtung (Commitment)
+Managementbewertung
+Anwendbare Richtlinien
+Umgang mit Nichtkonformitäten
+Kontinuierliche Verbesserung</t>
+  </si>
+  <si>
+    <t>Richtlinie für Informationssicherheitsbewusstsein und Schulungen</t>
+  </si>
+  <si>
+    <t>Auswirkungen bei Nichteinhaltung
+Meldung von Sicherheitsereignissen
+Kontinuierliche Verbesserung</t>
+  </si>
+  <si>
+    <t>Richtlinie für Arbeitsstationen und Telearbeit</t>
+  </si>
+  <si>
+    <t>Arbeitsstationen
+Mobile Geräte
+Telearbeit
+Passwortverwaltung
+Rückgabe von Assets
+Kontinuierliche Verbesserung</t>
+  </si>
+  <si>
+    <t>Kryptografierichtlinie</t>
+  </si>
+  <si>
+    <t>Schlüsselmanagement
+Verschlüsselung
+Kontinuierliche Verbesserung</t>
+  </si>
+  <si>
+    <t>Richtlinie zur Informationsklassifizierung und -handhabung</t>
+  </si>
+  <si>
+    <t>Klassifizierung
+Schutz und Handhabung von Informationen
+Schutz und Handhabung personenbezogener Daten (PII)
+Clean Desk
+Clean Screen
+Schutz von Aufzeichnungen
+Aufbewahrungsregeln
+Nutzung von Testinformationen
+Kontinuierliche Verbesserung</t>
+  </si>
+  <si>
+    <t>Interne und externe Auditrichtlinie</t>
+  </si>
+  <si>
+    <t>Schutz von Auditinformationen</t>
+  </si>
+  <si>
+    <t>Notfall- und Geschäftskontinuitätsrichtlinie</t>
+  </si>
+  <si>
+    <t>Richtlinie zur Funktionstrennung</t>
+  </si>
+  <si>
+    <t>Zugriffskontrollrichtlinie</t>
+  </si>
+  <si>
+    <t>Identifikation
+Authentifizierung
+Passwortmanagement
+RBAC (rollenbasierte Zugriffskontrolle)
+Überprüfung von Zugriffsrechten
+Provisionierung
+Austritte (Leavers)
+Remote Access
+Management privilegierter Zugänge
+Zugriff durch Dritte
+Überwachung und Berichterstattung
+Kontinuierliche Verbesserung</t>
+  </si>
+  <si>
+    <t>Informationssicherheitsrichtlinie</t>
+  </si>
+  <si>
+    <t>Richtlinie zum Schutz vor Schadsoftware</t>
+  </si>
+  <si>
+    <t>Antivirus
+EDR (Endpoint Detection and Response)</t>
+  </si>
+  <si>
+    <t>Risikomanagement-Richtlinie</t>
+  </si>
+  <si>
+    <t>Definition des Risikomanagements
+Risikobereitschaft (Risk Appetite)
+Kriterien zur Risikoakzeptanz
+Kriterien für die Risikobeurteilung
+Risikoidentifikation
+Risikobeurteilung
+CIAP-Ansatz
+Risikoberichterstattung
+Risikoüberprüfung
+Risikobehandlung (Risikominderung, Akzeptanz, Transfer)
+Risikobewertung
+Verwendung der ISO-27002-Kontrollen
+Verwaltung von Zugriffsrechten
+Kontinuierliche Verbesserung</t>
+  </si>
+  <si>
+    <t>Asset-Management-Richtlinie</t>
+  </si>
+  <si>
+    <t>Richtlinie zur Sicherung von Backups und Wiederherstellung</t>
+  </si>
+  <si>
+    <t>Sicherheitsrichtlinie für Lieferanten und Dritte</t>
+  </si>
+  <si>
+    <t>Richtlinie zu Logging und Monitoring</t>
+  </si>
+  <si>
+    <t>Richtlinie zum Informationsaustausch</t>
+  </si>
+  <si>
+    <t>Richtlinie für sichere Software- und Systementwicklung</t>
+  </si>
+  <si>
+    <t>Physische Sicherheitsrichtlinie</t>
+  </si>
+  <si>
+    <t>Physische Sicherheitsgrenzen
+Sicherheitsbereiche
+Zugangskontrolle für Mitarbeitende
+Zugangskontrolle für Besucher
+Management von Lieferungen
+Sicherung der Verkabelung
+Kontinuierliche Verbesserung</t>
+  </si>
+  <si>
+    <t>Richtlinie zum Management der Netzwerksicherheit</t>
+  </si>
+  <si>
+    <t>Richtlinie zur akzeptablen Nutzung (Acceptable Use Policy)</t>
+  </si>
+  <si>
+    <t>Zielsetzung: Definition der erlaubten und verbotenen Nutzung von Ressourcen.
+Geltungsbereich: Alle Benutzer der Informationssysteme.
+Regeln: Erlaubte und verbotene Aktivitäten, Sicherheitsverpflichtungen.
+Vertraulichkeit: Schutz sensibler Daten.
+Compliance: Überwachung, Sanktionen bei Nichtkonformität.</t>
+  </si>
+  <si>
+    <t>Richtlinie zur Integration von Sicherheit in IS-Projekte</t>
+  </si>
+  <si>
+    <t>Regeln für die Integration von Sicherheitsanforderungen in IS-Projekten</t>
+  </si>
+  <si>
+    <t>Threat-Intelligence-Richtlinie</t>
+  </si>
+  <si>
+    <t>Bekannte ausgenutzte Schwachstellen
+Aktivitäten von Bedrohungsakteuren
+Kontinuierliche Verbesserung</t>
+  </si>
+  <si>
+    <t>Richtlinie zum Management von Sicherheitsvorfällen (IS Incident Management Policy)</t>
+  </si>
+  <si>
+    <t>Klassifizierung von Sicherheitsvorfällen
+Meldung von Sicherheitsvorfällen
+Ablauf zur Incident Response
+Ursachenanalyse und Lessons Learned
+Dokumentation und Kommunikation
+Rollen und Verantwortlichkeiten
+Überprüfung und Aktualisierung</t>
+  </si>
+  <si>
+    <t>Wartungsrichtlinie</t>
+  </si>
+  <si>
+    <t>Management von Obsoleszenz
+Wartungsverträge
+Änderungsmanagement</t>
+  </si>
+  <si>
+    <t>Richtlinie zum Schwachstellenmanagement</t>
+  </si>
+  <si>
+    <t>Erkennung und Management von Schwachstellen
+Patch-Management</t>
+  </si>
+  <si>
+    <t>Schulung zu gesetzlichen und regulatorischen Anforderungen</t>
+  </si>
+  <si>
+    <t>Zielsetzung: Sicherstellung des Bewusstseins für gesetzliche und regulatorische Compliance.
+Zielgruppe: Alle Mitarbeitenden; spezifische Inhalte je nach Rolle.
+Themen: Wichtige Gesetze (z. B. DSGVO), Umgang mit Daten, Risiken bei Nichtkonformität.
+Methoden: E-Learning, Workshops, Fallstudien.
+Bewertung: Tests und szenariobasierte Prüfungen.</t>
+  </si>
+  <si>
+    <t>Schulung zur Bedrohungslage (Threat Landscape Training)</t>
+  </si>
+  <si>
+    <t>Zielsetzung: Verständnis aktueller Cyberbedrohungen und geeigneter Gegenmaßnahmen.
+Zielgruppe: IT-Personal, Sicherheitsteams und Entscheidungsträger.
+Themen: Neue Bedrohungen, Angriffstechniken, Verteidigungsmechanismen.
+Methoden: Präsentationen, Fallstudien, szenariobasierte Diskussionen.
+Ergebnis: Verbesserte Sensibilisierung und Bereitschaft, auf sich entwickelnde Bedrohungen zu reagieren.</t>
+  </si>
+  <si>
+    <t>Schulung zu Identity &amp; Access Management (IAM-Training)</t>
+  </si>
+  <si>
+    <t>Zielsetzung: Identitäts- und Zugriffsmanagement verstehen und sicher beherrschen.
+Zielgruppe: IT-Administratoren, Sicherheitsteams, Access-Manager.
+Themen:
+- Grundkonzepte (Identität, Authentifizierung, Autorisierung, RBAC/ABAC-Modelle)
+- IAM-Best Practices (Rechtemanagement, Provisionierung, Audits)
+- Standards und Werkzeuge (SAML, OAuth, Active Directory usw.)
+Methoden: Praktische Workshops, Use Cases, Demonstrationen.
+Ergebnis: Verbesserte Fähigkeiten zur sicheren und effizienten Verwaltung von Zugriffsrechten.</t>
+  </si>
+  <si>
+    <t>Schulung zur Netzwerksicherheit</t>
+  </si>
+  <si>
+    <t>Zielsetzung: Vermittlung bewährter Verfahren zur Absicherung der Netzwerkinfrastruktur und zur Abwehr von Cyberangriffen.
+Zielgruppe: IT-Administratoren, Netzwerkingenieure, Sicherheitsexperten.
+Themen:
+- Prinzipien der Netzwerksegmentierung
+- Konfiguration und Überwachung von Firewalls
+- Systeme zur Erkennung/Verhinderung von Angriffen (IDS/IPS/NDR)
+- Netzwerksegmentierung und Zugriffskontrolle
+- Sichere Protokolle (z. B. HTTPS, VPN, SSH)
+- Bedrohungsabwehr (z. B. DDoS, Malware)
+Methoden: Interaktive Labore, Simulationen, praktische Übungen.
+Ergebnis: Verbesserte Fähigkeit, Netzwerkumgebungen zu schützen und zu überwachen.</t>
+  </si>
+  <si>
+    <t>Zielsetzung: Aufbau von Fachwissen zur Sicherung von IT-Systemen durch Monitoring, Patch-Management, Compliance und Incident Response.
+Zielgruppe: IT-Sicherheitsfachkräfte, Systemadministratoren, Compliance-Beauftragte und Incident-Response-Teams.
+Themen:
+- Grundprinzipien der Aufrechterhaltung von Sicherheit und deren Bedeutung in der Cybersicherheit.
+- Werkzeuge und Techniken für Sicherheitsmonitoring (z. B. SIEM, IDS).
+- Patch-Management und sichere Systemkonfigurationen.
+- Erkennung von Sicherheitsvorfällen, Planung der Reaktion und Durchführung.
+- Einhaltung von Sicherheitsrichtlinien und regulatorischen Anforderungen.
+Methoden: Praktische Labore, simulierte Szenarien und Fallstudien zur Aufrechterhaltung sicherer Systemzustände.
+Ergebnis: Erweiterte Fähigkeit, IT-Umgebungen kontinuierlich zu sichern, Risiken zu reduzieren und Compliance sicherzustellen.</t>
+  </si>
+  <si>
+    <t>Schulung zu Logging und Monitoring</t>
+  </si>
+  <si>
+    <t>Schulung zur Aufrechterhaltung des sicheren Betriebs (MCS)</t>
+  </si>
+  <si>
+    <t>Security Condition Maintenance Training (SCM)</t>
+  </si>
+  <si>
+    <t>1. Zielsetzung: Vermittlung effektiver Protokollierungs- und Überwachungstechniken zur Verbesserung der Sicherheit und Incident Response.
+2. Zielgruppe: IT-Administratoren, Sicherheitsteams und SOC-Analysten.
+3. Themen:
+   - Bedeutung der Protokollierung und Compliance-Anforderungen.
+   - Konfiguration und Verwaltung von Log-Quellen (z. B. Server, Firewalls, Anwendungen).
+   - Zentrale Logging-Systeme (z. B. SIEM, ELK-Stack).
+   - Erkennung von Anomalien und Analyse von Logdaten.
+   - Incident Response auf Basis von Log-Informationen.
+4. Methoden: Praktische Übungen, realistische Szenarien und Aufgaben zur Log-Analyse.
+5. Ergebnis: Verbesserte Fähigkeit, Logdaten zu erfassen, zu analysieren und sicherheitsrelevante Maßnahmen abzuleiten.</t>
+  </si>
+  <si>
+    <t>Schulung zu Hardening und sicherer Konfiguration</t>
+  </si>
+  <si>
+    <t>Zielsetzung: Vermittlung von Wissen zur Umsetzung sicherer Konfigurationen und zur Härtung von Systemen, um Schwachstellen zu reduzieren.
+Zielgruppe: IT-Administratoren, Systemingenieure, Sicherheitsexperten.
+Themen:
+- Grundprinzipien der Systemhärtung.
+- Härtung von Betriebssystemen (Windows, Linux).
+- Sicherung von Datenbanken (z. B. MySQL, PostgreSQL).
+- Härtung von Netzwerkgeräten (Firewalls, Router, Switches).
+- Anwendung von CIS-Benchmarks und ANSSI-Richtlinien.
+- Werkzeuge für Automatisierung (z. B. Ansible, Puppet, Chef).
+Methoden:
+- Praktische Übungen zur Härtung von Betriebssystemen und Anwendungen.
+- Fallstudien zu Härtungsfehlern und deren Lösungen.
+Ergebnis: Teilnehmende können sichere Konfigurationen implementieren und die allgemeine Systemresilienz verbessern.</t>
+  </si>
+  <si>
+    <t>Eine Funktion, die sicherstellt, dass Geräte oder Benutzer vor der Gewährung von Netzwerkzugang authentifiziert und autorisiert werden. Sie ermöglicht sicheren Zugriff auf kabelgebundene und drahtlose Netzwerke, indem Protokolle wie 802.1X und RADIUS zur Validierung von Anmeldedaten und zur Durchsetzung von Zugriffskontrollrichtlinien verwendet werden.</t>
+  </si>
+  <si>
+    <t>Event-Detection- und Response-Kapazität (EDR)</t>
+  </si>
+  <si>
+    <t>Kapazität für Passwortmanagement</t>
+  </si>
+  <si>
+    <t>Eine Funktion, die die sichere Erstellung, Speicherung, Verwaltung und Nutzung von Passwörtern für Systeme, Anwendungen und Konten ermöglicht. Sie reduziert das Risiko unbefugter Zugriffe durch die Durchsetzung starker Passwortrichtlinien und eine sichere Handhabung von Zugangsdaten.</t>
+  </si>
+  <si>
+    <t>Unified Endpoint Management (UEM) – Fähigkeit</t>
+  </si>
+  <si>
+    <t>Eine Fähigkeit, die zentrale Steuerung und Verwaltung aller Endgeräte ermöglicht, einschließlich Desktop-Systemen, Laptops, Mobilgeräten und IoT-Geräten, über eine einheitliche Plattform. Sie gewährleistet sichere Konfigurationen, Richtlinienerzwingung, Anwendungsverwaltung sowie umfassendes Monitoring der gesamten Endgeräteumgebung einer Organisation.</t>
+  </si>
+  <si>
+    <t>Schutzmaßnahmen für Endgeräte (Antivirus, Firewall und USB-Kontrolle)</t>
+  </si>
+  <si>
+    <t>Integrierte Lösungen zur Absicherung von Endgeräten, einschließlich Antivirus-Schutz, Firewall-Kontrolle und Steuerung der USB-Ports.</t>
+  </si>
+  <si>
+    <t>Festplattenverschlüsselung</t>
+  </si>
+  <si>
+    <t>Vollständige Festplattenverschlüsselung für Arbeitsstationen.</t>
+  </si>
+  <si>
+    <t>Unveränderliche Backup-Kapazität (Immutable Backups)</t>
+  </si>
+  <si>
+    <t>Eine Fähigkeit, die sicherstellt, dass Backups nicht verändert, gelöscht oder überschrieben werden können, um die Datenintegrität gegen Ransomware und unbefugten Zugriff zu schützen.</t>
+  </si>
+  <si>
+    <t>Dateiverschlüsselungs-Kapazität</t>
+  </si>
+  <si>
+    <t>Dateiverschlüsselungswerkzeuge wie 7zip.</t>
+  </si>
+  <si>
+    <t>Configuration Management Database (CMDB)</t>
+  </si>
+  <si>
+    <t>Ein zentrales Repository, das Informationen über IT-Assets, deren Konfigurationen und Beziehungen speichert und verwaltet, um ein effektives IT-Management zu unterstützen.</t>
+  </si>
+  <si>
+    <t>Ein System, das Sicherheitsdaten aus mehreren Quellen sammelt, analysiert und korreliert, um Bedrohungen zu erkennen und darauf zu reagieren.</t>
+  </si>
+  <si>
+    <t>Blickschutzfilter (Screen Filter)</t>
+  </si>
+  <si>
+    <t>Ein physischer oder digitaler Filter, der die Sichtbarkeit von Bildschirminhalten für unbefugte Personen einschränkt und das Risiko visueller Datenlecks reduziert.</t>
+  </si>
+  <si>
+    <t>Netzwerk-Firewall</t>
+  </si>
+  <si>
+    <t>Netzwerk-Antivirus</t>
+  </si>
+  <si>
+    <t>Ein Sicherheitssystem, das auf Basis definierter Regeln eingehenden und ausgehenden Netzwerkverkehr überwacht und steuert.</t>
+  </si>
+  <si>
+    <t>Sicheres Mail-Gateway</t>
+  </si>
+  <si>
+    <t>Ein System, das E-Mail-Kommunikation filtert, überwacht und vor Spam, Malware und unbefugtem Zugriff schützt.</t>
+  </si>
+  <si>
+    <t>Schützt E-Mail- und Web-Verkehr am Netzwerkrand vor Malware.</t>
+  </si>
+  <si>
+    <t>VLANs isolieren und segmentieren Netzwerkverkehr, um Sicherheit und Leistungsfähigkeit zu verbessern.</t>
+  </si>
+  <si>
+    <t>Mikrosegmentierung</t>
+  </si>
+  <si>
+    <t>Eine Sicherheitsstrategie, die fein granulare, kontextbezogene Richtlinien erstellt, um einzelne Workloads oder Anwendungen innerhalb eines Netzwerks zu isolieren, laterale Bewegungen einzuschränken und Sicherheitsvorfälle einzudämmen.</t>
+  </si>
+  <si>
+    <t>WLAN-Sicherheit</t>
+  </si>
+  <si>
+    <t>WLAN-Sicherheit stellt geschützte drahtlose Kommunikation sicher, u. a. durch WPA3-Enterprise-Verschlüsselung, starke Authentifizierung und erweiterte Zugriffskontrollen. Obwohl WPA2-Enterprise weiterhin akzeptabel ist, wird der Umstieg auf WPA3 für erhöhte Sicherheit dringend empfohlen.</t>
+  </si>
+  <si>
+    <t>Ein Reverse Proxy leitet Client-Anfragen an Backend-Server weiter und verbessert dadurch Sicherheit, Lastverteilung und Performance.</t>
+  </si>
+  <si>
+    <t>Eine Web Application Firewall (WAF) schützt Webanwendungen, indem sie HTTP-Datenverkehr filtert und überwacht, um bösartige Aktivitäten zu blockieren.</t>
+  </si>
+  <si>
+    <t>Ein Intrusion Detection System überwacht Netzwerkverkehr, um potenzielle Sicherheitsbedrohungen oder unbefugte Aktivitäten zu erkennen und zu melden.</t>
+  </si>
+  <si>
+    <t>Web-Proxy</t>
+  </si>
+  <si>
+    <t>Ein Web-Proxy filtert und überwacht Web-Verkehr, erzwingt Sicherheitsrichtlinien und unterstützt Benutzer-Authentifizierung zur Kontrolle und Absicherung des Internetzugangs.</t>
+  </si>
+  <si>
+    <t>VPN (Virtual Private Network)</t>
+  </si>
+  <si>
+    <t>Ein Virtual Private Network (VPN) schützt Datenübertragungen durch Verschlüsselung mittels Protokollen wie IPSec und gewährleistet Privatsphäre sowie Schutz vor Abfangversuchen.</t>
+  </si>
+  <si>
+    <t>Multi-Faktor-Authentifizierung (MFA)</t>
+  </si>
+  <si>
+    <t>Die Multi-Faktor-Authentifizierung erhöht die Sicherheit, indem zwei oder mehr Verifizierungsfaktoren aus verschiedenen Kategorien verlangt werden: Wissen (z. B. Passwort), Besitz (z. B. Token oder Smartphone) und Biometrie (z. B. Fingerabdruck oder Gesichtserkennung).</t>
+  </si>
+  <si>
+    <t>© intuitem - 2026</t>
+  </si>
+  <si>
+    <t>Dokumentierter Plan für die Managementbewertung</t>
+  </si>
+  <si>
+    <t>DOC.INCIDENT_REGISTER</t>
+  </si>
+  <si>
+    <t>classification
+Protection and handling of information
+Protection and handling of PII
+clear desk
+clear screen
+Protection of records
+Retention rules
+Use of test information
+Continual improvement</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2158,7 +2846,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -2197,9 +2885,12 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -2499,14 +3190,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:B14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="76.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.140625" customWidth="1"/>
+    <col min="2" max="2" width="76.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2514,7 +3205,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -2522,84 +3213,100 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="16">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" t="s">
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
+      <c r="B5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" t="s">
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
+      <c r="B6" t="s">
         <v>10</v>
       </c>
-      <c r="B6" t="s">
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
+      <c r="B7" t="s">
         <v>12</v>
       </c>
-      <c r="B7" t="s">
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
+      <c r="B8" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
         <v>14</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B9" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
         <v>16</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
+      <c r="B11" t="s">
         <v>18</v>
       </c>
-      <c r="B10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
         <v>19</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B12" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>21</v>
-      </c>
-      <c r="B12" t="s">
-        <v>22</v>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>521</v>
+      </c>
+      <c r="B13" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
+        <v>522</v>
+      </c>
+      <c r="B14" t="s">
+        <v>524</v>
       </c>
     </row>
   </sheetData>
@@ -2610,26 +3317,26 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" t="s">
         <v>23</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B2" t="s">
-        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -2639,668 +3346,803 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:H28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:J28"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="22.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="42.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.83203125" customWidth="1"/>
-    <col min="5" max="5" width="70.33203125" customWidth="1"/>
-    <col min="6" max="6" width="20.83203125" customWidth="1"/>
-    <col min="7" max="7" width="17.5" customWidth="1"/>
-    <col min="8" max="8" width="73.1640625" customWidth="1"/>
+    <col min="1" max="1" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="42.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.28515625" customWidth="1"/>
+    <col min="4" max="4" width="14.85546875" customWidth="1"/>
+    <col min="5" max="5" width="70.28515625" customWidth="1"/>
+    <col min="6" max="6" width="20.85546875" customWidth="1"/>
+    <col min="7" max="7" width="17.42578125" customWidth="1"/>
+    <col min="8" max="8" width="73.140625" customWidth="1"/>
+    <col min="9" max="9" width="17.42578125" customWidth="1"/>
+    <col min="10" max="10" width="73.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" ht="31.5">
       <c r="A1" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="G1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="78.75">
+      <c r="A2" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F1" s="2" t="s">
+      <c r="B2" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G1" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="85" x14ac:dyDescent="0.2">
-      <c r="A2" s="4" t="s">
+      <c r="C2" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="D2" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="E2" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="F2" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="G2" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="H2" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="I2" t="s">
+        <v>525</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="63">
+      <c r="A3" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" ht="68" x14ac:dyDescent="0.2">
-      <c r="A3" s="4" t="s">
+      <c r="C3" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="F3" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E3" s="5" t="s">
+      <c r="G3" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="H3" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="I3" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="157.5">
+      <c r="A4" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="B4" s="4" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" ht="170" x14ac:dyDescent="0.2">
-      <c r="A4" s="4" t="s">
+      <c r="C4" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="F4" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E4" s="5" t="s">
+      <c r="G4" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="H4" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="I4" s="4" t="s">
+        <v>531</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="110.25">
+      <c r="A5" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="B5" s="5" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" ht="119" x14ac:dyDescent="0.2">
-      <c r="A5" s="4" t="s">
+      <c r="C5" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="F5" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="C5" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="E5" s="5" t="s">
+      <c r="G5" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="H5" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="I5" s="5" t="s">
+        <v>532</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="15.75">
+      <c r="A6" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="B6" s="4" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A6" s="4" t="s">
+      <c r="C6" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="I6" s="4" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="15.75">
+      <c r="A7" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="C6" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G6" s="4" t="s">
+      <c r="B7" s="4" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A7" s="4" t="s">
+      <c r="C7" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="F7" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="G7" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="C7" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="F7" s="4" t="s">
+      <c r="I7" s="4" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="173.25">
+      <c r="A8" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="B8" s="4" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" ht="187" x14ac:dyDescent="0.2">
-      <c r="A8" s="4" t="s">
+      <c r="C8" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="F8" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="C8" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="E8" s="5" t="s">
+      <c r="G8" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="H8" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="I8" s="4" t="s">
+        <v>535</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="15.75">
+      <c r="A9" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="B9" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A9" s="4" t="s">
+      <c r="C9" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="F9" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="G9" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="C9" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="F9" s="4" t="s">
+      <c r="I9" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="15.75">
+      <c r="A10" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="B10" s="4" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A10" s="4" t="s">
+      <c r="C10" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E10" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="G10" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="C10" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="E10" s="4" t="s">
+      <c r="H10" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="I10" t="s">
+        <v>538</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="15.75">
+      <c r="A11" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="H10" s="4" t="s">
+      <c r="B11" s="4" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A11" s="4" t="s">
+      <c r="C11" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="F11" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="G11" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="C11" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="F11" s="4" t="s">
+      <c r="I11" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="141.75">
+      <c r="A12" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="B12" s="4" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" ht="153" x14ac:dyDescent="0.2">
-      <c r="A12" s="4" t="s">
+      <c r="C12" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E12" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="F12" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="C12" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="E12" s="5" t="s">
+      <c r="G12" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="H12" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="I12" t="s">
+        <v>541</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="15.75">
+      <c r="A13" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="H12" s="5" t="s">
+      <c r="B13" s="4" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A13" s="4" t="s">
+      <c r="C13" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="F13" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="G13" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="C13" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="F13" s="9" t="s">
+      <c r="I13" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="78.75">
+      <c r="A14" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="G13" s="4" t="s">
+      <c r="B14" s="4" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" ht="85" x14ac:dyDescent="0.2">
-      <c r="A14" s="4" t="s">
+      <c r="C14" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E14" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="F14" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="C14" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="E14" s="5" t="s">
+      <c r="G14" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="H14" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="I14" s="4" t="s">
+        <v>684</v>
+      </c>
+      <c r="J14" s="5" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="31.5">
+      <c r="A15" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="H14" s="5" t="s">
+      <c r="B15" s="4" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" ht="34" x14ac:dyDescent="0.2">
-      <c r="A15" s="4" t="s">
+      <c r="C15" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="F15" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="G15" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="C15" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="F15" s="5" t="s">
+      <c r="I15" s="4" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="63">
+      <c r="A16" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="B16" s="4" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" ht="68" x14ac:dyDescent="0.2">
-      <c r="A16" s="4" t="s">
+      <c r="C16" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E16" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="F16" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="C16" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="E16" s="5" t="s">
+      <c r="G16" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="H16" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="I16" s="4" t="s">
+        <v>546</v>
+      </c>
+      <c r="J16" s="5" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="15.75">
+      <c r="A17" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="H16" s="5" t="s">
+      <c r="B17" s="4" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A17" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>108</v>
-      </c>
       <c r="C17" s="8" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="H17" s="5"/>
+      <c r="I17" s="4" t="s">
+        <v>548</v>
+      </c>
+      <c r="J17" s="5"/>
+    </row>
+    <row r="18" spans="1:10" ht="31.5">
+      <c r="A18" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="G17" s="4" t="s">
+      <c r="B18" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="H17" s="5"/>
-    </row>
-    <row r="18" spans="1:8" ht="34" x14ac:dyDescent="0.2">
-      <c r="A18" s="4" t="s">
+      <c r="C18" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E18" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="F18" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="C18" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="E18" s="5" t="s">
+      <c r="G18" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="F18" s="4" t="s">
+      <c r="H18" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="G18" s="4" t="s">
+      <c r="I18" s="4" t="s">
+        <v>549</v>
+      </c>
+      <c r="J18" s="5" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="15.75">
+      <c r="A19" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="H18" s="5" t="s">
+      <c r="B19" s="4" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A19" s="4" t="s">
+      <c r="C19" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="F19" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="G19" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="C19" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="F19" s="4" t="s">
+      <c r="I19" s="4" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="15.75">
+      <c r="A20" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="G19" s="4" t="s">
+      <c r="B20" s="4" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A20" s="4" t="s">
+      <c r="C20" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D20" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="F20" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="C20" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="D20" s="8" t="s">
+      <c r="G20" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="I20" s="4" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="15.75">
+      <c r="A21" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="G20" s="4" t="s">
+      <c r="B21" s="4" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A21" s="4" t="s">
+      <c r="C21" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="E21" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="G21" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="C21" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="E21" s="4" t="s">
+      <c r="H21" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="G21" s="4" t="s">
+      <c r="I21" s="4" t="s">
+        <v>553</v>
+      </c>
+      <c r="J21" s="4" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="315">
+      <c r="A22" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="H21" s="4" t="s">
+      <c r="B22" s="4" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" ht="289" x14ac:dyDescent="0.2">
-      <c r="A22" s="4" t="s">
+      <c r="C22" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E22" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="F22" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="C22" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="E22" s="5" t="s">
+      <c r="G22" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="F22" s="5" t="s">
+      <c r="H22" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="G22" s="4" t="s">
+      <c r="I22" s="4" t="s">
+        <v>555</v>
+      </c>
+      <c r="J22" s="5" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="141.75">
+      <c r="A23" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="H22" s="5" t="s">
+      <c r="B23" s="4" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" ht="136" x14ac:dyDescent="0.2">
-      <c r="A23" s="4" t="s">
+      <c r="C23" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E23" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="F23" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="C23" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="E23" s="5" t="s">
+      <c r="G23" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="F23" s="4" t="s">
+      <c r="H23" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="G23" s="4" t="s">
+      <c r="I23" s="4" t="s">
+        <v>557</v>
+      </c>
+      <c r="J23" s="5" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="47.25">
+      <c r="A24" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="H23" s="5" t="s">
+      <c r="B24" s="4" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" ht="34" x14ac:dyDescent="0.2">
-      <c r="A24" s="4" t="s">
+      <c r="C24" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="E24" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="F24" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="G24" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="C24" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="E24" s="5" t="s">
+      <c r="H24" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="F24" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="G24" s="4" t="s">
+      <c r="I24" s="4" t="s">
+        <v>559</v>
+      </c>
+      <c r="J24" s="5" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="15.75">
+      <c r="A25" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="H24" s="5" t="s">
+      <c r="B25" s="5" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A25" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>149</v>
-      </c>
       <c r="C25" s="8" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E25" s="5"/>
       <c r="F25" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="I25" s="4" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="47.25">
+      <c r="A26" s="4" t="s">
+        <v>685</v>
+      </c>
+      <c r="B26" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="G25" s="4" t="s">
+      <c r="C26" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D26" s="8" t="s">
         <v>151</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="51" x14ac:dyDescent="0.2">
-      <c r="A26" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="D26" s="8" t="s">
-        <v>154</v>
       </c>
       <c r="E26" s="5"/>
       <c r="F26" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="I26" s="5" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="47.25">
+      <c r="A27" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="B27" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="G26" s="5" t="s">
+      <c r="C27" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="E27" s="5" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" ht="34" x14ac:dyDescent="0.2">
-      <c r="A27" s="4" t="s">
+      <c r="F27" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="G27" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="C27" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="D27" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="E27" s="5" t="s">
+      <c r="H27" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="F27" s="4" t="s">
+      <c r="I27" s="4" t="s">
+        <v>563</v>
+      </c>
+      <c r="J27" s="5" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="15.75">
+      <c r="A28" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="G27" s="4" t="s">
+      <c r="B28" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="H27" s="5" t="s">
+      <c r="C28" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D28" s="8" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A28" s="4" t="s">
+      <c r="F28" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="G28" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="C28" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="D28" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="G28" s="4" t="s">
-        <v>167</v>
+      <c r="I28" s="4" t="s">
+        <v>565</v>
       </c>
     </row>
   </sheetData>
@@ -3311,25 +4153,25 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" t="s">
         <v>23</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B2" t="s">
-        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -3339,329 +4181,403 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:H12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:J12"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="23.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="70.83203125" customWidth="1"/>
+    <col min="3" max="3" width="9.28515625" customWidth="1"/>
+    <col min="4" max="4" width="11.140625" customWidth="1"/>
+    <col min="5" max="5" width="70.85546875" customWidth="1"/>
     <col min="6" max="6" width="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="37.1640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="86.33203125" customWidth="1"/>
+    <col min="7" max="7" width="37.140625" customWidth="1"/>
+    <col min="8" max="8" width="86.28515625" customWidth="1"/>
+    <col min="9" max="9" width="37.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="86.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" ht="31.5">
       <c r="A1" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>28</v>
-      </c>
       <c r="G1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H1" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="68" x14ac:dyDescent="0.2">
+      <c r="I1" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="63">
       <c r="A2" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="F2" s="5" t="s">
         <v>294</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>295</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="H2" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="D2" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="E2" s="5" t="s">
+      <c r="I2" s="4" t="s">
+        <v>566</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="78.75">
+      <c r="A3" s="4" t="s">
         <v>297</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>298</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="C3" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="F3" s="4" t="s">
         <v>300</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" ht="85" x14ac:dyDescent="0.2">
-      <c r="A3" s="4" t="s">
+      <c r="G3" s="4" t="s">
         <v>301</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="H3" s="5" t="s">
         <v>302</v>
       </c>
-      <c r="C3" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="E3" s="5" t="s">
+      <c r="I3" s="4" t="s">
+        <v>568</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="78.75">
+      <c r="A4" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="B4" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="C4" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>305</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="F4" s="5" t="s">
         <v>306</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" ht="68" x14ac:dyDescent="0.2">
-      <c r="A4" s="4" t="s">
+      <c r="G4" s="5" t="s">
         <v>307</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="H4" s="5" t="s">
         <v>308</v>
       </c>
-      <c r="C4" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="E4" s="5" t="s">
+      <c r="I4" s="5" t="s">
+        <v>570</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="157.5">
+      <c r="A5" s="4" t="s">
         <v>309</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="B5" s="4" t="s">
         <v>310</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="C5" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="5" t="s">
         <v>311</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="F5" s="5" t="s">
         <v>312</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" ht="170" x14ac:dyDescent="0.2">
-      <c r="A5" s="4" t="s">
+      <c r="G5" s="4" t="s">
         <v>313</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="H5" s="5" t="s">
         <v>314</v>
       </c>
-      <c r="C5" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="E5" s="5" t="s">
+      <c r="I5" s="4" t="s">
+        <v>572</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="63">
+      <c r="A6" s="4" t="s">
         <v>315</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="B6" s="4" t="s">
         <v>316</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="C6" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="E6" s="5" t="s">
         <v>317</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="F6" s="4" t="s">
         <v>318</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" ht="68" x14ac:dyDescent="0.2">
-      <c r="A6" s="4" t="s">
+      <c r="G6" s="4" t="s">
         <v>319</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="H6" s="5" t="s">
         <v>320</v>
       </c>
-      <c r="C6" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="E6" s="5" t="s">
+      <c r="I6" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="110.25">
+      <c r="A7" s="4" t="s">
         <v>321</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="B7" s="4" t="s">
         <v>322</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="C7" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="E7" s="5" t="s">
         <v>323</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="F7" s="4" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" ht="119" x14ac:dyDescent="0.2">
-      <c r="A7" s="4" t="s">
+      <c r="G7" s="5" t="s">
         <v>325</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="H7" s="5" t="s">
         <v>326</v>
       </c>
-      <c r="C7" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="E7" s="5" t="s">
+      <c r="I7" s="5" t="s">
+        <v>576</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="78.75">
+      <c r="A8" s="4" t="s">
         <v>327</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="B8" s="4" t="s">
         <v>328</v>
       </c>
-      <c r="G7" s="5" t="s">
+      <c r="C8" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="E8" s="5" t="s">
         <v>329</v>
       </c>
-      <c r="H7" s="5" t="s">
+      <c r="F8" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="G8" s="4" t="s">
         <v>330</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" ht="85" x14ac:dyDescent="0.2">
-      <c r="A8" s="4" t="s">
+      <c r="H8" s="5" t="s">
         <v>331</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="I8" s="4" t="s">
+        <v>578</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="110.25">
+      <c r="A9" s="4" t="s">
         <v>332</v>
       </c>
-      <c r="C8" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="E8" s="5" t="s">
+      <c r="B9" s="4" t="s">
         <v>333</v>
       </c>
-      <c r="F8" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="G8" s="4" t="s">
+      <c r="C9" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="E9" s="5" t="s">
         <v>334</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="F9" s="5" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" ht="119" x14ac:dyDescent="0.2">
-      <c r="A9" s="4" t="s">
+      <c r="G9" s="4" t="s">
         <v>336</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="H9" s="5" t="s">
         <v>337</v>
       </c>
-      <c r="C9" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="E9" s="5" t="s">
+      <c r="I9" s="4" t="s">
+        <v>580</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="63">
+      <c r="A10" s="4" t="s">
         <v>338</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="B10" s="4" t="s">
         <v>339</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="C10" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="E10" s="5" t="s">
         <v>340</v>
       </c>
-      <c r="H9" s="5" t="s">
+      <c r="F10" s="5" t="s">
         <v>341</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" ht="68" x14ac:dyDescent="0.2">
-      <c r="A10" s="4" t="s">
+      <c r="G10" s="4" t="s">
         <v>342</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="H10" s="5" t="s">
         <v>343</v>
       </c>
-      <c r="C10" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="E10" s="5" t="s">
+      <c r="I10" s="4" t="s">
+        <v>582</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="110.25">
+      <c r="A11" s="4" t="s">
         <v>344</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="B11" s="4" t="s">
         <v>345</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="C11" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="E11" s="5" t="s">
         <v>346</v>
       </c>
-      <c r="H10" s="5" t="s">
+      <c r="F11" s="5" t="s">
         <v>347</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" ht="119" x14ac:dyDescent="0.2">
-      <c r="A11" s="4" t="s">
+      <c r="G11" s="4" t="s">
         <v>348</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="H11" s="5" t="s">
         <v>349</v>
       </c>
-      <c r="C11" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="E11" s="5" t="s">
+      <c r="I11" s="4" t="s">
+        <v>584</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="47.25">
+      <c r="A12" s="4" t="s">
         <v>350</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="B12" s="4" t="s">
         <v>351</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="C12" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="D12" s="8" t="s">
         <v>352</v>
       </c>
-      <c r="H11" s="5" t="s">
+      <c r="E12" s="5" t="s">
         <v>353</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" ht="51" x14ac:dyDescent="0.2">
-      <c r="A12" s="4" t="s">
+      <c r="F12" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="G12" s="4" t="s">
         <v>354</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="H12" s="5" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>356</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>357</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>241</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>358</v>
-      </c>
-      <c r="H12" s="5" t="s">
-        <v>359</v>
+      <c r="I12" s="4" t="s">
+        <v>586</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>587</v>
       </c>
     </row>
   </sheetData>
@@ -3672,25 +4588,25 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" t="s">
         <v>23</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B2" t="s">
-        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -3700,637 +4616,770 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:H27"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:J27"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="43.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.33203125" customWidth="1"/>
-    <col min="4" max="4" width="21.1640625" customWidth="1"/>
-    <col min="5" max="5" width="55.33203125" customWidth="1"/>
-    <col min="6" max="6" width="27.1640625" customWidth="1"/>
-    <col min="7" max="7" width="23.6640625" customWidth="1"/>
-    <col min="8" max="8" width="70.33203125" customWidth="1"/>
+    <col min="2" max="2" width="43.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="21.140625" customWidth="1"/>
+    <col min="5" max="5" width="55.28515625" customWidth="1"/>
+    <col min="6" max="6" width="27.140625" customWidth="1"/>
+    <col min="7" max="7" width="23.7109375" customWidth="1"/>
+    <col min="8" max="8" width="70.28515625" customWidth="1"/>
+    <col min="9" max="9" width="23.7109375" customWidth="1"/>
+    <col min="10" max="10" width="70.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" ht="15.75">
       <c r="A1" s="10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C1" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>28</v>
-      </c>
       <c r="G1" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="H1" s="10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="102" x14ac:dyDescent="0.2">
+      <c r="I1" s="10" t="s">
+        <v>521</v>
+      </c>
+      <c r="J1" s="10" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="94.5">
       <c r="A2" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="F2" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="G2" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="D2" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="E2" s="5" t="s">
+      <c r="H2" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="I2" s="5" t="s">
+        <v>603</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="63">
+      <c r="A3" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="C3" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" ht="51" x14ac:dyDescent="0.2">
-      <c r="A3" s="4" t="s">
+      <c r="F3" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="G3" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="E3" s="5" t="s">
+      <c r="H3" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="I3" s="5" t="s">
+        <v>589</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="94.5">
+      <c r="A4" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="B4" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="C4" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" ht="102" x14ac:dyDescent="0.2">
-      <c r="A4" s="4" t="s">
+      <c r="F4" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="G4" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="E4" s="5" t="s">
+      <c r="H4" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="I4" s="5" t="s">
+        <v>591</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="47.25">
+      <c r="A5" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="B5" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="C5" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="5" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" ht="51" x14ac:dyDescent="0.2">
-      <c r="A5" s="4" t="s">
+      <c r="F5" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="G5" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="E5" s="5" t="s">
+      <c r="H5" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="I5" s="5" t="s">
+        <v>593</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="141.75">
+      <c r="A6" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="B6" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="C6" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>686</v>
+      </c>
+      <c r="F6" s="5" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" ht="153" x14ac:dyDescent="0.2">
-      <c r="A6" s="4" t="s">
+      <c r="G6" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="H6" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="E6" s="5" t="s">
+      <c r="I6" s="5" t="s">
+        <v>595</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="31.5">
+      <c r="A7" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="B7" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="C7" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="F7" s="5" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" ht="34" x14ac:dyDescent="0.2">
-      <c r="A7" s="4" t="s">
+      <c r="G7" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="H7" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="E7" s="4" t="s">
+      <c r="I7" s="5" t="s">
+        <v>597</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="47.25">
+      <c r="A8" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="B8" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="G7" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="34" x14ac:dyDescent="0.2">
-      <c r="A8" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>206</v>
-      </c>
       <c r="C8" s="4" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F8" s="5"/>
       <c r="G8" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="31.5">
+      <c r="A9" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="G9" s="5" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" ht="34" x14ac:dyDescent="0.2">
-      <c r="A9" s="4" t="s">
+      <c r="I9" s="5" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="189">
+      <c r="A10" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B10" s="4" t="s">
         <v>209</v>
       </c>
-      <c r="C9" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="F9" s="5" t="s">
+      <c r="C10" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E10" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="G9" s="5" t="s">
+      <c r="F10" s="5" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" ht="204" x14ac:dyDescent="0.2">
-      <c r="A10" s="4" t="s">
+      <c r="G10" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="H10" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="C10" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="E10" s="5" t="s">
+      <c r="I10" s="5" t="s">
+        <v>601</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="47.25">
+      <c r="A11" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="B11" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="G10" s="5" t="s">
+      <c r="C11" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E11" s="5" t="s">
         <v>216</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="51" x14ac:dyDescent="0.2">
-      <c r="A11" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>220</v>
       </c>
       <c r="F11" s="5"/>
       <c r="G11" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>604</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="220.5">
+      <c r="A12" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="F12" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="H11" s="5" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="238" x14ac:dyDescent="0.2">
-      <c r="A12" s="4" t="s">
+      <c r="G12" s="5" t="s">
         <v>222</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="H12" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="C12" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="E12" s="5" t="s">
+      <c r="I12" s="5" t="s">
+        <v>606</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="31.5">
+      <c r="A13" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="B13" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="G12" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="H12" s="5" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="34" x14ac:dyDescent="0.2">
-      <c r="A13" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>229</v>
-      </c>
       <c r="C13" s="8" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F13" s="5"/>
       <c r="G13" s="5" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+        <v>226</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="47.25">
       <c r="A14" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F14" s="5"/>
       <c r="G14" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="31.5">
+      <c r="A15" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="G15" s="5" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" ht="34" x14ac:dyDescent="0.2">
-      <c r="A15" s="4" t="s">
+      <c r="I15" s="5" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="47.25">
+      <c r="A16" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B16" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="C15" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="F15" s="5" t="s">
+      <c r="C16" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E16" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="G15" s="5" t="s">
+      <c r="F16" s="5" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" ht="34" x14ac:dyDescent="0.2">
-      <c r="A16" s="4" t="s">
+      <c r="G16" s="5" t="s">
         <v>238</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="H16" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="C16" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="E16" s="4" t="s">
+      <c r="I16" s="5" t="s">
+        <v>611</v>
+      </c>
+      <c r="J16" s="4"/>
+    </row>
+    <row r="17" spans="1:10" ht="31.5">
+      <c r="A17" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="F16" s="5" t="s">
+      <c r="B17" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="G16" s="5" t="s">
+      <c r="C17" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="F17" s="5" t="s">
         <v>242</v>
       </c>
-      <c r="H16" s="4" t="s">
+      <c r="G17" s="5" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" ht="34" x14ac:dyDescent="0.2">
-      <c r="A17" s="4" t="s">
+      <c r="I17" s="5" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="47.25">
+      <c r="A18" s="4" t="s">
         <v>244</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B18" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="C17" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>246</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="34" x14ac:dyDescent="0.2">
-      <c r="A18" s="4" t="s">
-        <v>248</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>249</v>
-      </c>
       <c r="C18" s="8" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F18" s="5"/>
       <c r="G18" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="110.25">
+      <c r="A19" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="G19" s="5" t="s">
         <v>250</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" ht="119" x14ac:dyDescent="0.2">
-      <c r="A19" s="4" t="s">
+      <c r="H19" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="I19" s="5" t="s">
+        <v>614</v>
+      </c>
+      <c r="J19" s="5" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="47.25">
+      <c r="A20" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="C19" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="E19" s="5" t="s">
+      <c r="B20" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="F19" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="H19" s="5" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="34" x14ac:dyDescent="0.2">
-      <c r="A20" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>257</v>
-      </c>
       <c r="C20" s="8" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F20" s="5"/>
       <c r="G20" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="110.25">
+      <c r="A21" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="F21" s="5" t="s">
         <v>258</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" ht="102" x14ac:dyDescent="0.2">
-      <c r="A21" s="4" t="s">
+      <c r="G21" s="5" t="s">
         <v>259</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="H21" s="5" t="s">
         <v>260</v>
       </c>
-      <c r="C21" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="E21" s="5" t="s">
+      <c r="I21" s="5" t="s">
+        <v>617</v>
+      </c>
+      <c r="J21" s="5" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="47.25">
+      <c r="A22" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="F21" s="5" t="s">
+      <c r="B22" s="4" t="s">
         <v>262</v>
       </c>
-      <c r="G21" s="5" t="s">
+      <c r="C22" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E22" s="4" t="s">
         <v>263</v>
       </c>
-      <c r="H21" s="5" t="s">
+      <c r="F22" s="5" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" ht="34" x14ac:dyDescent="0.2">
-      <c r="A22" s="4" t="s">
+      <c r="G22" s="5" t="s">
         <v>265</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="H22" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="C22" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="E22" s="4" t="s">
+      <c r="I22" s="5" t="s">
+        <v>619</v>
+      </c>
+      <c r="J22" s="4" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="47.25">
+      <c r="A23" s="4" t="s">
         <v>267</v>
       </c>
-      <c r="F22" s="5" t="s">
+      <c r="B23" s="4" t="s">
         <v>268</v>
       </c>
-      <c r="G22" s="5" t="s">
+      <c r="C23" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E23" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="H22" s="4" t="s">
+      <c r="F23" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="G23" s="5" t="s">
         <v>270</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" ht="51" x14ac:dyDescent="0.2">
-      <c r="A23" s="4" t="s">
+      <c r="H23" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="I23" s="5" t="s">
+        <v>621</v>
+      </c>
+      <c r="J23" s="5" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="110.25">
+      <c r="A24" s="4" t="s">
         <v>272</v>
       </c>
-      <c r="C23" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="E23" s="5" t="s">
+      <c r="B24" s="4" t="s">
         <v>273</v>
       </c>
-      <c r="F23" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="G23" s="5" t="s">
+      <c r="C24" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E24" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="H23" s="5" t="s">
+      <c r="F24" s="5" t="s">
         <v>275</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" ht="119" x14ac:dyDescent="0.2">
-      <c r="A24" s="4" t="s">
+      <c r="G24" s="5" t="s">
         <v>276</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="H24" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="C24" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="E24" s="5" t="s">
+      <c r="I24" s="5" t="s">
+        <v>623</v>
+      </c>
+      <c r="J24" s="5" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="47.25">
+      <c r="A25" s="4" t="s">
         <v>278</v>
       </c>
-      <c r="F24" s="5" t="s">
+      <c r="B25" s="4" t="s">
         <v>279</v>
       </c>
-      <c r="G24" s="5" t="s">
+      <c r="C25" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E25" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="H24" s="5" t="s">
+      <c r="F25" s="5" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" ht="51" x14ac:dyDescent="0.2">
-      <c r="A25" s="4" t="s">
+      <c r="G25" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="H25" s="5" t="s">
         <v>283</v>
       </c>
-      <c r="C25" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="E25" s="5" t="s">
+      <c r="I25" s="5" t="s">
+        <v>625</v>
+      </c>
+      <c r="J25" s="5" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="47.25">
+      <c r="A26" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="F25" s="5" t="s">
+      <c r="B26" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="G25" s="5" t="s">
+      <c r="C26" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E26" s="5" t="s">
         <v>286</v>
       </c>
-      <c r="H25" s="5" t="s">
+      <c r="F26" s="5" t="s">
         <v>287</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" ht="34" x14ac:dyDescent="0.2">
-      <c r="A26" s="4" t="s">
+      <c r="G26" s="5" t="s">
         <v>288</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="H26" s="5" t="s">
         <v>289</v>
       </c>
-      <c r="C26" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="D26" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>290</v>
-      </c>
-      <c r="F26" s="5" t="s">
-        <v>291</v>
-      </c>
-      <c r="G26" s="5" t="s">
-        <v>292</v>
-      </c>
-      <c r="H26" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I26" s="5" t="s">
+        <v>627</v>
+      </c>
+      <c r="J26" s="5" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="15.75">
       <c r="G27" s="5"/>
+      <c r="I27" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4340,25 +5389,25 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" t="s">
         <v>23</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B2" t="s">
-        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -4368,834 +5417,1025 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:H32"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:J32"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="26.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="44.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.83203125" customWidth="1"/>
-    <col min="5" max="5" width="73.1640625" customWidth="1"/>
-    <col min="6" max="6" width="15.83203125" customWidth="1"/>
-    <col min="7" max="7" width="52.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="44.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.42578125" customWidth="1"/>
+    <col min="4" max="4" width="16.85546875" customWidth="1"/>
+    <col min="5" max="5" width="46.28515625" customWidth="1"/>
+    <col min="6" max="6" width="15.85546875" customWidth="1"/>
+    <col min="7" max="7" width="52.85546875" customWidth="1"/>
     <col min="8" max="8" width="82" customWidth="1"/>
+    <col min="9" max="9" width="41.42578125" customWidth="1"/>
+    <col min="10" max="10" width="82" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" ht="31.5">
       <c r="A1" s="11" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>28</v>
-      </c>
       <c r="G1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H1" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="85" x14ac:dyDescent="0.2">
+      <c r="I1" s="3" t="s">
+        <v>521</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="110.25">
       <c r="A2" s="12" t="s">
+        <v>356</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>357</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>358</v>
+      </c>
+      <c r="F2" s="13" t="s">
+        <v>359</v>
+      </c>
+      <c r="G2" s="12" t="s">
         <v>360</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="H2" s="13" t="s">
         <v>361</v>
       </c>
-      <c r="C2" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="D2" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="E2" s="13" t="s">
+      <c r="I2" s="12" t="s">
+        <v>629</v>
+      </c>
+      <c r="J2" s="13" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="157.5">
+      <c r="A3" s="12" t="s">
         <v>362</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="B3" s="12" t="s">
         <v>363</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="C3" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" s="13" t="s">
         <v>364</v>
       </c>
-      <c r="H2" s="13" t="s">
+      <c r="F3" s="13" t="s">
+        <v>359</v>
+      </c>
+      <c r="G3" s="14" t="s">
         <v>365</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" ht="85" x14ac:dyDescent="0.2">
-      <c r="A3" s="12" t="s">
+      <c r="H3" s="13" t="s">
         <v>366</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="I3" s="14" t="s">
+        <v>631</v>
+      </c>
+      <c r="J3" s="13" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="236.25">
+      <c r="A4" s="12" t="s">
         <v>367</v>
       </c>
-      <c r="C3" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="D3" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="E3" s="13" t="s">
+      <c r="B4" s="12" t="s">
         <v>368</v>
       </c>
-      <c r="F3" s="13" t="s">
-        <v>363</v>
-      </c>
-      <c r="G3" s="14" t="s">
+      <c r="C4" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" s="13" t="s">
         <v>369</v>
       </c>
-      <c r="H3" s="13" t="s">
+      <c r="F4" s="12" t="s">
         <v>370</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" ht="136" x14ac:dyDescent="0.2">
-      <c r="A4" s="12" t="s">
+      <c r="G4" s="12" t="s">
         <v>371</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="H4" s="13" t="s">
         <v>372</v>
       </c>
-      <c r="C4" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="D4" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="E4" s="13" t="s">
+      <c r="I4" s="12" t="s">
+        <v>633</v>
+      </c>
+      <c r="J4" s="13" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="267.75">
+      <c r="A5" s="12" t="s">
         <v>373</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="B5" s="12" t="s">
         <v>374</v>
       </c>
-      <c r="G4" s="12" t="s">
+      <c r="C5" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="13" t="s">
         <v>375</v>
       </c>
-      <c r="H4" s="13" t="s">
+      <c r="F5" s="12" t="s">
+        <v>370</v>
+      </c>
+      <c r="G5" s="12" t="s">
         <v>376</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" ht="221" x14ac:dyDescent="0.2">
-      <c r="A5" s="12" t="s">
+      <c r="H5" s="13" t="s">
         <v>377</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="I5" s="12" t="s">
+        <v>635</v>
+      </c>
+      <c r="J5" s="13" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="362.25">
+      <c r="A6" s="12" t="s">
         <v>378</v>
       </c>
-      <c r="C5" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="E5" s="13" t="s">
+      <c r="B6" s="12" t="s">
+        <v>640</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" s="13" t="s">
         <v>379</v>
       </c>
-      <c r="F5" s="12" t="s">
-        <v>374</v>
-      </c>
-      <c r="G5" s="12" t="s">
+      <c r="F6" s="13" t="s">
+        <v>281</v>
+      </c>
+      <c r="G6" s="13" t="s">
         <v>380</v>
       </c>
-      <c r="H5" s="13" t="s">
+      <c r="H6" s="13" t="s">
         <v>381</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" ht="238" x14ac:dyDescent="0.2">
-      <c r="A6" s="12" t="s">
+      <c r="I6" s="13" t="s">
+        <v>639</v>
+      </c>
+      <c r="J6" s="13" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="299.25">
+      <c r="A7" s="12" t="s">
         <v>382</v>
       </c>
-      <c r="C6" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="E6" s="13" t="s">
+      <c r="B7" s="12" t="s">
         <v>383</v>
       </c>
-      <c r="F6" s="13" t="s">
-        <v>285</v>
-      </c>
-      <c r="G6" s="13" t="s">
+      <c r="C7" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" s="13" t="s">
         <v>384</v>
       </c>
-      <c r="H6" s="13" t="s">
+      <c r="F7" s="13" t="s">
         <v>385</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" ht="204" x14ac:dyDescent="0.2">
-      <c r="A7" s="12" t="s">
+      <c r="G7" s="12" t="s">
         <v>386</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="H7" s="13" t="s">
         <v>387</v>
       </c>
-      <c r="C7" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="E7" s="13" t="s">
+      <c r="I7" s="12" t="s">
+        <v>638</v>
+      </c>
+      <c r="J7" s="13" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="393.75">
+      <c r="A8" s="12" t="s">
         <v>388</v>
       </c>
-      <c r="F7" s="13" t="s">
+      <c r="B8" s="12" t="s">
         <v>389</v>
       </c>
-      <c r="G7" s="12" t="s">
+      <c r="C8" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8" s="13" t="s">
         <v>390</v>
       </c>
-      <c r="H7" s="13" t="s">
+      <c r="F8" s="13" t="s">
         <v>391</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" ht="255" x14ac:dyDescent="0.2">
-      <c r="A8" s="12" t="s">
+      <c r="G8" s="12" t="s">
         <v>392</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="H8" s="13" t="s">
         <v>393</v>
       </c>
-      <c r="C8" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="D8" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="E8" s="13" t="s">
+      <c r="I8" s="12" t="s">
+        <v>642</v>
+      </c>
+      <c r="J8" s="13" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="94.5">
+      <c r="A9" s="12" t="s">
         <v>394</v>
       </c>
-      <c r="F8" s="13" t="s">
+      <c r="B9" s="12" t="s">
         <v>395</v>
       </c>
-      <c r="G8" s="12" t="s">
+      <c r="C9" s="12" t="s">
         <v>396</v>
       </c>
-      <c r="H8" s="13" t="s">
+      <c r="D9" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="E9" s="13" t="s">
         <v>397</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" ht="68" x14ac:dyDescent="0.2">
-      <c r="A9" s="12" t="s">
+      <c r="F9" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="G9" s="12" t="s">
         <v>398</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="H9" s="13" t="s">
         <v>399</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="I9" s="12" t="s">
+        <v>395</v>
+      </c>
+      <c r="J9" s="13" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="31.5">
+      <c r="A10" s="12" t="s">
         <v>400</v>
       </c>
-      <c r="D9" s="12" t="s">
-        <v>165</v>
-      </c>
-      <c r="E9" s="13" t="s">
+      <c r="B10" s="12" t="s">
         <v>401</v>
       </c>
-      <c r="F9" s="12" t="s">
-        <v>160</v>
-      </c>
-      <c r="G9" s="12" t="s">
+      <c r="C10" s="12" t="s">
+        <v>396</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>352</v>
+      </c>
+      <c r="F10" s="13" t="s">
         <v>402</v>
       </c>
-      <c r="H9" s="13" t="s">
+      <c r="G10" s="12" t="s">
         <v>403</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" ht="34" x14ac:dyDescent="0.2">
-      <c r="A10" s="12" t="s">
+      <c r="I10" s="12" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="31.5">
+      <c r="A11" s="12" t="s">
         <v>404</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B11" s="12" t="s">
         <v>405</v>
       </c>
-      <c r="C10" s="12" t="s">
-        <v>400</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>356</v>
-      </c>
-      <c r="F10" s="13" t="s">
+      <c r="C11" s="12" t="s">
+        <v>396</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>352</v>
+      </c>
+      <c r="F11" s="13" t="s">
+        <v>402</v>
+      </c>
+      <c r="G11" s="12" t="s">
         <v>406</v>
       </c>
-      <c r="G10" s="12" t="s">
+      <c r="I11" s="12" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="94.5">
+      <c r="A12" s="12" t="s">
         <v>407</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" ht="34" x14ac:dyDescent="0.2">
-      <c r="A11" s="12" t="s">
+      <c r="B12" s="12" t="s">
         <v>408</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="C12" s="12" t="s">
+        <v>396</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="E12" s="13" t="s">
         <v>409</v>
       </c>
-      <c r="C11" s="12" t="s">
-        <v>400</v>
-      </c>
-      <c r="D11" s="12" t="s">
-        <v>356</v>
-      </c>
-      <c r="F11" s="13" t="s">
-        <v>406</v>
-      </c>
-      <c r="G11" s="12" t="s">
+      <c r="F12" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="G12" s="12" t="s">
         <v>410</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" ht="68" x14ac:dyDescent="0.2">
-      <c r="A12" s="12" t="s">
+      <c r="H12" s="13" t="s">
         <v>411</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="I12" s="12" t="s">
+        <v>646</v>
+      </c>
+      <c r="J12" s="13" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="110.25">
+      <c r="A13" s="12" t="s">
         <v>412</v>
       </c>
-      <c r="C12" s="12" t="s">
-        <v>400</v>
-      </c>
-      <c r="D12" s="12" t="s">
-        <v>165</v>
-      </c>
-      <c r="E12" s="13" t="s">
+      <c r="B13" s="12" t="s">
         <v>413</v>
       </c>
-      <c r="F12" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="G12" s="12" t="s">
+      <c r="C13" s="12" t="s">
+        <v>396</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="E13" s="13" t="s">
         <v>414</v>
       </c>
-      <c r="H12" s="13" t="s">
+      <c r="F13" s="12" t="s">
+        <v>318</v>
+      </c>
+      <c r="G13" s="12" t="s">
         <v>415</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" ht="68" x14ac:dyDescent="0.2">
-      <c r="A13" s="12" t="s">
+      <c r="H13" s="13" t="s">
         <v>416</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="I13" s="12" t="s">
+        <v>648</v>
+      </c>
+      <c r="J13" s="13" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="47.25">
+      <c r="A14" s="12" t="s">
         <v>417</v>
       </c>
-      <c r="C13" s="12" t="s">
-        <v>400</v>
-      </c>
-      <c r="D13" s="12" t="s">
-        <v>165</v>
-      </c>
-      <c r="E13" s="13" t="s">
+      <c r="B14" s="12" t="s">
         <v>418</v>
       </c>
-      <c r="F13" s="12" t="s">
-        <v>322</v>
-      </c>
-      <c r="G13" s="12" t="s">
+      <c r="C14" s="12" t="s">
+        <v>396</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>352</v>
+      </c>
+      <c r="E14" s="13" t="s">
         <v>419</v>
       </c>
-      <c r="H13" s="13" t="s">
+      <c r="F14" s="12" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" ht="34" x14ac:dyDescent="0.2">
-      <c r="A14" s="12" t="s">
+      <c r="G14" s="12" t="s">
         <v>421</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="H14" s="13" t="s">
         <v>422</v>
       </c>
-      <c r="C14" s="12" t="s">
-        <v>400</v>
-      </c>
-      <c r="D14" s="12" t="s">
-        <v>356</v>
-      </c>
-      <c r="E14" s="13" t="s">
+      <c r="I14" s="12" t="s">
+        <v>650</v>
+      </c>
+      <c r="J14" s="13" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="15.75">
+      <c r="A15" s="12" t="s">
         <v>423</v>
       </c>
-      <c r="F14" s="12" t="s">
+      <c r="B15" s="12" t="s">
         <v>424</v>
       </c>
-      <c r="G14" s="12" t="s">
+      <c r="C15" s="12" t="s">
+        <v>396</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="E15" s="12" t="s">
         <v>425</v>
       </c>
-      <c r="H14" s="13" t="s">
+      <c r="F15" s="13" t="s">
         <v>426</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A15" s="12" t="s">
+      <c r="G15" s="12" t="s">
         <v>427</v>
       </c>
-      <c r="B15" s="12" t="s">
+      <c r="H15" s="12" t="s">
         <v>428</v>
       </c>
-      <c r="C15" s="12" t="s">
-        <v>400</v>
-      </c>
-      <c r="D15" s="12" t="s">
-        <v>165</v>
-      </c>
-      <c r="E15" s="12" t="s">
+      <c r="I15" s="12" t="s">
+        <v>652</v>
+      </c>
+      <c r="J15" s="12" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="63">
+      <c r="A16" s="12" t="s">
         <v>429</v>
       </c>
-      <c r="F15" s="13" t="s">
+      <c r="B16" s="12" t="s">
         <v>430</v>
       </c>
-      <c r="G15" s="12" t="s">
+      <c r="C16" s="12" t="s">
+        <v>396</v>
+      </c>
+      <c r="D16" s="12" t="s">
         <v>431</v>
       </c>
-      <c r="H15" s="12" t="s">
+      <c r="E16" s="13" t="s">
         <v>432</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" ht="34" x14ac:dyDescent="0.2">
-      <c r="A16" s="12" t="s">
+      <c r="F16" s="12" t="s">
         <v>433</v>
       </c>
-      <c r="B16" s="12" t="s">
+      <c r="G16" s="13" t="s">
         <v>434</v>
       </c>
-      <c r="C16" s="12" t="s">
-        <v>400</v>
-      </c>
-      <c r="D16" s="12" t="s">
+      <c r="H16" s="13" t="s">
         <v>435</v>
       </c>
-      <c r="E16" s="13" t="s">
+      <c r="I16" s="13" t="s">
+        <v>654</v>
+      </c>
+      <c r="J16" s="13" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="15.75">
+      <c r="A17" s="12" t="s">
         <v>436</v>
       </c>
-      <c r="F16" s="12" t="s">
+      <c r="B17" s="12" t="s">
         <v>437</v>
       </c>
-      <c r="G16" s="13" t="s">
+      <c r="C17" s="12" t="s">
+        <v>396</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="E17" s="12" t="s">
         <v>438</v>
       </c>
-      <c r="H16" s="13" t="s">
+      <c r="F17" s="12" t="s">
+        <v>426</v>
+      </c>
+      <c r="G17" s="12" t="s">
         <v>439</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A17" s="12" t="s">
+      <c r="H17" s="12" t="s">
         <v>440</v>
       </c>
-      <c r="B17" s="12" t="s">
+      <c r="I17" s="12" t="s">
+        <v>656</v>
+      </c>
+      <c r="J17" s="12" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="63">
+      <c r="A18" s="12" t="s">
         <v>441</v>
       </c>
-      <c r="C17" s="12" t="s">
-        <v>400</v>
-      </c>
-      <c r="D17" s="12" t="s">
-        <v>165</v>
-      </c>
-      <c r="E17" s="12" t="s">
+      <c r="B18" s="12" t="s">
         <v>442</v>
       </c>
-      <c r="F17" s="12" t="s">
-        <v>430</v>
-      </c>
-      <c r="G17" s="12" t="s">
+      <c r="C18" s="12" t="s">
+        <v>396</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="E18" s="13" t="s">
         <v>443</v>
       </c>
-      <c r="H17" s="12" t="s">
+      <c r="F18" s="12" t="s">
+        <v>318</v>
+      </c>
+      <c r="G18" s="13" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" ht="34" x14ac:dyDescent="0.2">
-      <c r="A18" s="12" t="s">
+      <c r="H18" s="13" t="s">
         <v>445</v>
       </c>
-      <c r="B18" s="12" t="s">
+      <c r="I18" s="13" t="s">
+        <v>658</v>
+      </c>
+      <c r="J18" s="13" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="63">
+      <c r="A19" s="12" t="s">
         <v>446</v>
       </c>
-      <c r="C18" s="12" t="s">
-        <v>400</v>
-      </c>
-      <c r="D18" s="12" t="s">
-        <v>123</v>
-      </c>
-      <c r="E18" s="13" t="s">
+      <c r="B19" s="12" t="s">
         <v>447</v>
       </c>
-      <c r="F18" s="12" t="s">
-        <v>322</v>
-      </c>
-      <c r="G18" s="13" t="s">
+      <c r="C19" s="12" t="s">
+        <v>396</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>352</v>
+      </c>
+      <c r="E19" s="13" t="s">
         <v>448</v>
       </c>
-      <c r="H18" s="13" t="s">
+      <c r="F19" s="12" t="s">
         <v>449</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" ht="51" x14ac:dyDescent="0.2">
-      <c r="A19" s="12" t="s">
+      <c r="G19" s="13" t="s">
         <v>450</v>
       </c>
-      <c r="B19" s="12" t="s">
+      <c r="H19" s="13" t="s">
         <v>451</v>
       </c>
-      <c r="C19" s="12" t="s">
-        <v>400</v>
-      </c>
-      <c r="D19" s="12" t="s">
-        <v>356</v>
-      </c>
-      <c r="E19" s="13" t="s">
+      <c r="I19" s="13" t="s">
+        <v>447</v>
+      </c>
+      <c r="J19" s="13" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="47.25">
+      <c r="A20" s="12" t="s">
         <v>452</v>
       </c>
-      <c r="F19" s="12" t="s">
+      <c r="B20" s="12" t="s">
         <v>453</v>
       </c>
-      <c r="G19" s="13" t="s">
+      <c r="C20" s="12" t="s">
+        <v>396</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="E20" s="13" t="s">
         <v>454</v>
       </c>
-      <c r="H19" s="13" t="s">
+      <c r="F20" s="12" t="s">
         <v>455</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" ht="34" x14ac:dyDescent="0.2">
-      <c r="A20" s="12" t="s">
+      <c r="G20" s="12" t="s">
         <v>456</v>
       </c>
-      <c r="B20" s="12" t="s">
+      <c r="H20" s="13" t="s">
         <v>457</v>
       </c>
-      <c r="C20" s="12" t="s">
-        <v>400</v>
-      </c>
-      <c r="D20" s="12" t="s">
-        <v>165</v>
-      </c>
-      <c r="E20" s="13" t="s">
+      <c r="I20" s="12" t="s">
+        <v>661</v>
+      </c>
+      <c r="J20" s="13" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="47.25">
+      <c r="A21" s="12" t="s">
         <v>458</v>
       </c>
-      <c r="F20" s="12" t="s">
+      <c r="B21" s="12" t="s">
         <v>459</v>
       </c>
-      <c r="G20" s="12" t="s">
+      <c r="C21" s="12" t="s">
+        <v>396</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="E21" s="13" t="s">
         <v>460</v>
       </c>
-      <c r="H20" s="13" t="s">
+      <c r="F21" s="12" t="s">
         <v>461</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" ht="34" x14ac:dyDescent="0.2">
-      <c r="A21" s="12" t="s">
+      <c r="G21" s="12" t="s">
         <v>462</v>
       </c>
-      <c r="B21" s="12" t="s">
+      <c r="H21" s="13" t="s">
         <v>463</v>
       </c>
-      <c r="C21" s="12" t="s">
-        <v>400</v>
-      </c>
-      <c r="D21" s="12" t="s">
-        <v>165</v>
-      </c>
-      <c r="E21" s="13" t="s">
+      <c r="I21" s="12" t="s">
+        <v>663</v>
+      </c>
+      <c r="J21" s="13" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="47.25">
+      <c r="A22" s="13" t="s">
         <v>464</v>
       </c>
-      <c r="F21" s="12" t="s">
+      <c r="B22" s="12" t="s">
         <v>465</v>
       </c>
-      <c r="G21" s="12" t="s">
+      <c r="C22" s="12" t="s">
+        <v>396</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="E22" s="13" t="s">
         <v>466</v>
       </c>
-      <c r="H21" s="13" t="s">
+      <c r="F22" s="12" t="s">
+        <v>318</v>
+      </c>
+      <c r="G22" s="12" t="s">
         <v>467</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" ht="34" x14ac:dyDescent="0.2">
-      <c r="A22" s="13" t="s">
+      <c r="H22" s="13" t="s">
         <v>468</v>
       </c>
-      <c r="B22" s="12" t="s">
+      <c r="I22" s="12" t="s">
+        <v>666</v>
+      </c>
+      <c r="J22" s="13" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="31.5">
+      <c r="A23" s="15" t="s">
         <v>469</v>
       </c>
-      <c r="C22" s="12" t="s">
-        <v>400</v>
-      </c>
-      <c r="D22" s="12" t="s">
-        <v>165</v>
-      </c>
-      <c r="E22" s="13" t="s">
+      <c r="B23" s="12" t="s">
         <v>470</v>
       </c>
-      <c r="F22" s="12" t="s">
-        <v>322</v>
-      </c>
-      <c r="G22" s="12" t="s">
+      <c r="C23" s="12" t="s">
+        <v>396</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>352</v>
+      </c>
+      <c r="E23" s="13" t="s">
         <v>471</v>
       </c>
-      <c r="H22" s="13" t="s">
+      <c r="F23" s="12" t="s">
+        <v>420</v>
+      </c>
+      <c r="G23" s="12" t="s">
         <v>472</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A23" s="15" t="s">
+      <c r="H23" s="13" t="s">
         <v>473</v>
       </c>
-      <c r="B23" s="12" t="s">
+      <c r="I23" s="12" t="s">
+        <v>664</v>
+      </c>
+      <c r="J23" s="13" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="31.5">
+      <c r="A24" s="13" t="s">
         <v>474</v>
       </c>
-      <c r="C23" s="12" t="s">
-        <v>400</v>
-      </c>
-      <c r="D23" s="12" t="s">
-        <v>356</v>
-      </c>
-      <c r="E23" s="13" t="s">
+      <c r="B24" s="12" t="s">
         <v>475</v>
       </c>
-      <c r="F23" s="12" t="s">
-        <v>424</v>
-      </c>
-      <c r="G23" s="12" t="s">
+      <c r="C24" s="12" t="s">
+        <v>396</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="E24" s="13" t="s">
         <v>476</v>
       </c>
-      <c r="H23" s="13" t="s">
+      <c r="F24" s="12" t="s">
+        <v>461</v>
+      </c>
+      <c r="G24" s="12" t="s">
+        <v>475</v>
+      </c>
+      <c r="H24" s="13" t="s">
         <v>477</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" ht="34" x14ac:dyDescent="0.2">
-      <c r="A24" s="13" t="s">
+      <c r="I24" s="12" t="s">
+        <v>475</v>
+      </c>
+      <c r="J24" s="13" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="78.75">
+      <c r="A25" s="12" t="s">
         <v>478</v>
       </c>
-      <c r="B24" s="12" t="s">
+      <c r="B25" s="12" t="s">
         <v>479</v>
       </c>
-      <c r="C24" s="12" t="s">
-        <v>400</v>
-      </c>
-      <c r="D24" s="12" t="s">
-        <v>165</v>
-      </c>
-      <c r="E24" s="13" t="s">
+      <c r="C25" s="12" t="s">
+        <v>396</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="E25" s="13" t="s">
         <v>480</v>
       </c>
-      <c r="F24" s="12" t="s">
-        <v>465</v>
-      </c>
-      <c r="G24" s="12" t="s">
-        <v>479</v>
-      </c>
-      <c r="H24" s="13" t="s">
+      <c r="F25" s="12" t="s">
+        <v>461</v>
+      </c>
+      <c r="G25" s="12" t="s">
         <v>481</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" ht="51" x14ac:dyDescent="0.2">
-      <c r="A25" s="12" t="s">
+      <c r="H25" s="13" t="s">
         <v>482</v>
       </c>
-      <c r="B25" s="12" t="s">
+      <c r="I25" s="12" t="s">
+        <v>670</v>
+      </c>
+      <c r="J25" s="13" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="110.25">
+      <c r="A26" s="13" t="s">
         <v>483</v>
       </c>
-      <c r="C25" s="12" t="s">
-        <v>400</v>
-      </c>
-      <c r="D25" s="12" t="s">
-        <v>165</v>
-      </c>
-      <c r="E25" s="13" t="s">
+      <c r="B26" s="12" t="s">
         <v>484</v>
       </c>
-      <c r="F25" s="12" t="s">
-        <v>465</v>
-      </c>
-      <c r="G25" s="12" t="s">
+      <c r="C26" s="12" t="s">
+        <v>396</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="E26" s="13" t="s">
         <v>485</v>
       </c>
-      <c r="H25" s="13" t="s">
+      <c r="F26" s="13" t="s">
         <v>486</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" ht="68" x14ac:dyDescent="0.2">
-      <c r="A26" s="13" t="s">
+      <c r="G26" s="12" t="s">
         <v>487</v>
       </c>
-      <c r="B26" s="12" t="s">
+      <c r="H26" s="13" t="s">
         <v>488</v>
       </c>
-      <c r="C26" s="12" t="s">
-        <v>400</v>
-      </c>
-      <c r="D26" s="12" t="s">
-        <v>165</v>
-      </c>
-      <c r="E26" s="13" t="s">
+      <c r="I26" s="12" t="s">
+        <v>672</v>
+      </c>
+      <c r="J26" s="13" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="47.25">
+      <c r="A27" s="12" t="s">
         <v>489</v>
       </c>
-      <c r="F26" s="13" t="s">
+      <c r="B27" s="12" t="s">
         <v>490</v>
       </c>
-      <c r="G26" s="12" t="s">
+      <c r="C27" s="12" t="s">
+        <v>396</v>
+      </c>
+      <c r="D27" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="E27" s="13" t="s">
         <v>491</v>
       </c>
-      <c r="H26" s="13" t="s">
+      <c r="F27" s="12" t="s">
         <v>492</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" ht="34" x14ac:dyDescent="0.2">
-      <c r="A27" s="12" t="s">
+      <c r="G27" s="12" t="s">
         <v>493</v>
       </c>
-      <c r="B27" s="12" t="s">
+      <c r="H27" s="13" t="s">
         <v>494</v>
       </c>
-      <c r="C27" s="12" t="s">
-        <v>400</v>
-      </c>
-      <c r="D27" s="12" t="s">
-        <v>165</v>
-      </c>
-      <c r="E27" s="13" t="s">
+      <c r="I27" s="12" t="s">
+        <v>490</v>
+      </c>
+      <c r="J27" s="13" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="47.25">
+      <c r="A28" s="12" t="s">
         <v>495</v>
       </c>
-      <c r="F27" s="12" t="s">
+      <c r="B28" s="12" t="s">
         <v>496</v>
       </c>
-      <c r="G27" s="12" t="s">
+      <c r="C28" s="12" t="s">
+        <v>396</v>
+      </c>
+      <c r="D28" s="12" t="s">
+        <v>352</v>
+      </c>
+      <c r="E28" s="13" t="s">
         <v>497</v>
       </c>
-      <c r="H27" s="13" t="s">
+      <c r="F28" s="12" t="s">
+        <v>492</v>
+      </c>
+      <c r="G28" s="12" t="s">
         <v>498</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" ht="34" x14ac:dyDescent="0.2">
-      <c r="A28" s="12" t="s">
+      <c r="H28" s="13" t="s">
         <v>499</v>
       </c>
-      <c r="B28" s="12" t="s">
+      <c r="I28" s="12" t="s">
+        <v>496</v>
+      </c>
+      <c r="J28" s="13" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="47.25">
+      <c r="A29" s="12" t="s">
         <v>500</v>
       </c>
-      <c r="C28" s="12" t="s">
-        <v>400</v>
-      </c>
-      <c r="D28" s="12" t="s">
-        <v>356</v>
-      </c>
-      <c r="E28" s="13" t="s">
+      <c r="B29" s="12" t="s">
         <v>501</v>
       </c>
-      <c r="F28" s="12" t="s">
-        <v>496</v>
-      </c>
-      <c r="G28" s="12" t="s">
+      <c r="C29" s="12" t="s">
+        <v>396</v>
+      </c>
+      <c r="D29" s="12" t="s">
+        <v>352</v>
+      </c>
+      <c r="E29" s="13" t="s">
         <v>502</v>
       </c>
-      <c r="H28" s="13" t="s">
+      <c r="F29" s="12" t="s">
         <v>503</v>
       </c>
-    </row>
-    <row r="29" spans="1:8" ht="34" x14ac:dyDescent="0.2">
-      <c r="A29" s="12" t="s">
+      <c r="G29" s="12" t="s">
         <v>504</v>
       </c>
-      <c r="B29" s="12" t="s">
+      <c r="H29" s="13" t="s">
         <v>505</v>
       </c>
-      <c r="C29" s="12" t="s">
-        <v>400</v>
-      </c>
-      <c r="D29" s="12" t="s">
-        <v>356</v>
-      </c>
-      <c r="E29" s="13" t="s">
+      <c r="I29" s="12" t="s">
+        <v>501</v>
+      </c>
+      <c r="J29" s="13" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="63">
+      <c r="A30" s="13" t="s">
         <v>506</v>
       </c>
-      <c r="F29" s="12" t="s">
+      <c r="B30" s="12" t="s">
         <v>507</v>
       </c>
-      <c r="G29" s="12" t="s">
+      <c r="C30" s="12" t="s">
+        <v>396</v>
+      </c>
+      <c r="D30" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="E30" s="13" t="s">
         <v>508</v>
       </c>
-      <c r="H29" s="13" t="s">
+      <c r="F30" s="12" t="s">
+        <v>492</v>
+      </c>
+      <c r="G30" s="12" t="s">
         <v>509</v>
       </c>
-    </row>
-    <row r="30" spans="1:8" ht="34" x14ac:dyDescent="0.2">
-      <c r="A30" s="13" t="s">
+      <c r="H30" s="13" t="s">
         <v>510</v>
       </c>
-      <c r="B30" s="12" t="s">
+      <c r="I30" s="12" t="s">
+        <v>677</v>
+      </c>
+      <c r="J30" s="13" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="63">
+      <c r="A31" s="12" t="s">
         <v>511</v>
       </c>
-      <c r="C30" s="12" t="s">
-        <v>400</v>
-      </c>
-      <c r="D30" s="12" t="s">
-        <v>165</v>
-      </c>
-      <c r="E30" s="13" t="s">
+      <c r="B31" s="12" t="s">
         <v>512</v>
       </c>
-      <c r="F30" s="12" t="s">
-        <v>496</v>
-      </c>
-      <c r="G30" s="12" t="s">
+      <c r="C31" s="12" t="s">
+        <v>396</v>
+      </c>
+      <c r="D31" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="E31" s="13" t="s">
         <v>513</v>
       </c>
-      <c r="H30" s="13" t="s">
+      <c r="F31" s="13" t="s">
+        <v>486</v>
+      </c>
+      <c r="G31" s="12" t="s">
+        <v>512</v>
+      </c>
+      <c r="H31" s="13" t="s">
         <v>514</v>
       </c>
-    </row>
-    <row r="31" spans="1:8" ht="51" x14ac:dyDescent="0.2">
-      <c r="A31" s="12" t="s">
+      <c r="I31" s="12" t="s">
+        <v>679</v>
+      </c>
+      <c r="J31" s="13" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="94.5">
+      <c r="A32" s="12" t="s">
         <v>515</v>
       </c>
-      <c r="B31" s="12" t="s">
+      <c r="B32" s="12" t="s">
         <v>516</v>
       </c>
-      <c r="C31" s="12" t="s">
-        <v>400</v>
-      </c>
-      <c r="D31" s="12" t="s">
-        <v>165</v>
-      </c>
-      <c r="E31" s="13" t="s">
+      <c r="C32" s="12" t="s">
+        <v>396</v>
+      </c>
+      <c r="D32" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="E32" s="13" t="s">
         <v>517</v>
       </c>
-      <c r="F31" s="13" t="s">
-        <v>490</v>
-      </c>
-      <c r="G31" s="12" t="s">
-        <v>516</v>
-      </c>
-      <c r="H31" s="13" t="s">
+      <c r="F32" s="12" t="s">
         <v>518</v>
       </c>
-    </row>
-    <row r="32" spans="1:8" ht="68" x14ac:dyDescent="0.2">
-      <c r="A32" s="12" t="s">
+      <c r="G32" s="12" t="s">
         <v>519</v>
       </c>
-      <c r="B32" s="12" t="s">
+      <c r="H32" s="13" t="s">
         <v>520</v>
       </c>
-      <c r="C32" s="12" t="s">
-        <v>400</v>
-      </c>
-      <c r="D32" s="12" t="s">
-        <v>165</v>
-      </c>
-      <c r="E32" s="13" t="s">
-        <v>521</v>
-      </c>
-      <c r="F32" s="12" t="s">
-        <v>522</v>
-      </c>
-      <c r="G32" s="12" t="s">
-        <v>523</v>
-      </c>
-      <c r="H32" s="13" t="s">
-        <v>524</v>
+      <c r="I32" s="12" t="s">
+        <v>681</v>
+      </c>
+      <c r="J32" s="13" t="s">
+        <v>682</v>
       </c>
     </row>
   </sheetData>
